--- a/CTS/PaperTwoSyllabus.xlsx
+++ b/CTS/PaperTwoSyllabus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyNotes\CTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D78D739B-2E71-4CFE-8E2F-3730890F71F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0D27318-7D19-4838-A4EC-565B8FC0BE78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{9261B8EF-00DF-4F81-805E-634D14888222}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{9261B8EF-00DF-4F81-805E-634D14888222}"/>
   </bookViews>
   <sheets>
     <sheet name="422" sheetId="1" r:id="rId1"/>
@@ -556,9 +556,6 @@
 materials, Engineering ceramics, Engineering and commodity polymers, composites, nano-materials. </t>
   </si>
   <si>
-    <t>Manufacturing Process and Industrial Engineering (20 Questions)</t>
-  </si>
-  <si>
     <t>Foundry Technology, Metal Forming Processes –Manufacturing of Thermo Setting and Thermo Plastic
 Products, Machinability machine tools - center lathe, drilling, milling, grinding, gear cutting and
 broaching, Machining Time Calculation, unconventional machining processes, CNC machine tools,
@@ -630,6 +627,9 @@
       </rPr>
       <t xml:space="preserve"> — 554 Unit 9 = 566 Unit 8</t>
     </r>
+  </si>
+  <si>
+    <t>b</t>
   </si>
 </sst>
 </file>
@@ -1408,10 +1408,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1430,7 +1430,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
@@ -1438,22 +1438,22 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
